--- a/artfynd/A 41414-2024 artfynd.xlsx
+++ b/artfynd/A 41414-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120829533</v>
+        <v>120820315</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,17 +949,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Villola V, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619994</v>
+        <v>619996</v>
       </c>
       <c r="R4" t="n">
-        <v>6970182</v>
+        <v>6970177</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,19 +986,9 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,22 +1003,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120820315</v>
+        <v>120829533</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,17 +1051,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Villola V, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619996</v>
+        <v>619994</v>
       </c>
       <c r="R5" t="n">
-        <v>6970177</v>
+        <v>6970182</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,9 +1088,19 @@
           <t>2024-11-02</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,12 +1115,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1130,7 +1130,7 @@
         <v>120820086</v>
       </c>
       <c r="B6" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120820231</v>
+        <v>120829529</v>
       </c>
       <c r="B7" t="n">
-        <v>57348</v>
+        <v>74708</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,42 +1245,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Villola V, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>619983</v>
+        <v>620073</v>
       </c>
       <c r="R7" t="n">
-        <v>6970164</v>
+        <v>6970254</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,9 +1302,19 @@
           <t>2024-11-02</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,22 +1329,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120829527</v>
+        <v>120819994</v>
       </c>
       <c r="B8" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,17 +1377,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Villola V, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620062</v>
+        <v>619950</v>
       </c>
       <c r="R8" t="n">
-        <v>6970299</v>
+        <v>6970188</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,19 +1414,9 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:07</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,22 +1431,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120819994</v>
+        <v>120820231</v>
       </c>
       <c r="B9" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,34 +1459,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619950</v>
+        <v>619983</v>
       </c>
       <c r="R9" t="n">
-        <v>6970188</v>
+        <v>6970164</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120829526</v>
+        <v>120820090</v>
       </c>
       <c r="B10" t="n">
-        <v>78598</v>
+        <v>79642</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,41 +1562,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Villola V, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620063</v>
+        <v>619983</v>
       </c>
       <c r="R10" t="n">
-        <v>6970322</v>
+        <v>6970164</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1623,19 +1623,9 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1650,22 +1640,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120829523</v>
+        <v>120829526</v>
       </c>
       <c r="B11" t="n">
-        <v>57501</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,43 +1668,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Villola V, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620018</v>
+        <v>620063</v>
       </c>
       <c r="R11" t="n">
-        <v>6970382</v>
+        <v>6970322</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1756,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120829528</v>
+        <v>120829523</v>
       </c>
       <c r="B12" t="n">
-        <v>90705</v>
+        <v>57504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1799,34 +1780,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Villola V, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620057</v>
+        <v>620018</v>
       </c>
       <c r="R12" t="n">
-        <v>6970252</v>
+        <v>6970382</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1858,7 +1848,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1868,7 +1858,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,10 +1885,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120829529</v>
+        <v>120829527</v>
       </c>
       <c r="B13" t="n">
-        <v>74705</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,21 +1901,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1935,10 +1925,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620073</v>
+        <v>620062</v>
       </c>
       <c r="R13" t="n">
-        <v>6970254</v>
+        <v>6970299</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,7 +1960,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1980,7 +1970,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120820090</v>
+        <v>120829528</v>
       </c>
       <c r="B14" t="n">
-        <v>79639</v>
+        <v>90715</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,41 +2009,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Villola V, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619983</v>
+        <v>620057</v>
       </c>
       <c r="R14" t="n">
-        <v>6970164</v>
+        <v>6970252</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2080,9 +2070,19 @@
           <t>2024-11-02</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2097,12 +2097,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 41414-2024 artfynd.xlsx
+++ b/artfynd/A 41414-2024 artfynd.xlsx
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120820231</v>
+        <v>120829526</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,42 +1459,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Ång</t>
+          <t>Villola V, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619983</v>
+        <v>620063</v>
       </c>
       <c r="R9" t="n">
-        <v>6970164</v>
+        <v>6970322</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1521,9 +1516,19 @@
           <t>2024-11-02</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,22 +1543,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120820090</v>
+        <v>120820231</v>
       </c>
       <c r="B10" t="n">
-        <v>79642</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,28 +1567,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Ång</t>
@@ -1652,10 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120829526</v>
+        <v>120820090</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>79642</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1664,41 +1674,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Villola V, Ång</t>
+          <t>Brännan, Brännan, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620063</v>
+        <v>619983</v>
       </c>
       <c r="R11" t="n">
-        <v>6970322</v>
+        <v>6970164</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1725,19 +1735,9 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,12 +1752,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
